--- a/home_inspection_forms/032_exterior_door_replacement_survey--home_inspection_forms.xlsx
+++ b/home_inspection_forms/032_exterior_door_replacement_survey--home_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'refurbish'}</t>
+          <t>refurbish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Refurbish'}</t>
+          <t>Refurbish</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'replace'}</t>
+          <t>replace</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Replace'}</t>
+          <t>Replace</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'door_hardware'}</t>
+          <t>door_hardware</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Door Hardware'}</t>
+          <t>Door Hardware</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'door_frame'}</t>
+          <t>door_frame</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Door Frame'}</t>
+          <t>Door Frame</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'door_handle'}</t>
+          <t>door_handle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Door Handle'}</t>
+          <t>Door Handle</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'exterior'}</t>
+          <t>exterior</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Exterior'}</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'interior'}</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Interior'}</t>
+          <t>Interior</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'solid_core'}</t>
+          <t>solid_core</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Solid Core'}</t>
+          <t>Solid Core</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'hollow_core'}</t>
+          <t>hollow_core</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Hollow Core'}</t>
+          <t>Hollow Core</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'wood_frame'}</t>
+          <t>wood_frame</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Wood Frame'}</t>
+          <t>Wood Frame</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'metal_frame'}</t>
+          <t>metal_frame</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Metal Frame'}</t>
+          <t>Metal Frame</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'fiberglass_frame'}</t>
+          <t>fiberglass_frame</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Fiberglass Frame'}</t>
+          <t>Fiberglass Frame</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'insulated_glass'}</t>
+          <t>insulated_glass</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Insulated Glass'}</t>
+          <t>Insulated Glass</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'low-e_glass'}</t>
+          <t>low-e_glass</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Low-E Glass'}</t>
+          <t>Low-E Glass</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'low-e_+_insulated_glass'}</t>
+          <t>low-e_+_insulated_glass</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Low-E + Insulated Glass'}</t>
+          <t>Low-E + Insulated Glass</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'30"'}</t>
+          <t>30"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '30"'}</t>
+          <t>30"</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'36"'}</t>
+          <t>36"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': '36"'}</t>
+          <t>36"</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'48"'}</t>
+          <t>48"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '48"'}</t>
+          <t>48"</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'60"'}</t>
+          <t>60"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '60"'}</t>
+          <t>60"</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'wood'}</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Wood'}</t>
+          <t>Wood</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'vinyl'}</t>
+          <t>vinyl</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Vinyl'}</t>
+          <t>Vinyl</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'aluminum'}</t>
+          <t>aluminum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Aluminum'}</t>
+          <t>Aluminum</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'hinges'}</t>
+          <t>hinges</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Hinges'}</t>
+          <t>Hinges</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'no_hinges'}</t>
+          <t>no_hinges</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'No Hinges'}</t>
+          <t>No Hinges</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'magnetic'}</t>
+          <t>magnetic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Magnetic'}</t>
+          <t>Magnetic</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'lever_handle'}</t>
+          <t>lever_handle</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Lever Handle'}</t>
+          <t>Lever Handle</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'knob_handle'}</t>
+          <t>knob_handle</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Knob Handle'}</t>
+          <t>Knob Handle</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'lever_&amp;_knob'}</t>
+          <t>lever_&amp;_knob</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Lever &amp; Knob'}</t>
+          <t>Lever &amp; Knob</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'deadbolt'}</t>
+          <t>deadbolt</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Deadbolt'}</t>
+          <t>Deadbolt</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'dummy'}</t>
+          <t>dummy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Dummy'}</t>
+          <t>Dummy</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'lock_and_deadbolt'}</t>
+          <t>lock_and_deadbolt</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Lock and Deadbolt'}</t>
+          <t>Lock and Deadbolt</t>
         </is>
       </c>
     </row>
